--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2db1a885ed34419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R259f3f3ba5194420"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R259f3f3ba5194420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc7fd9efa124946f6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc7fd9efa124946f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e3145b51ea34278"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e3145b51ea34278"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b2e0d85535c49a0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b2e0d85535c49a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf901928313964cc7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf901928313964cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd4323a290bff4803"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd4323a290bff4803"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R686d588fe54b469c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R686d588fe54b469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ae8d328630740cf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ae8d328630740cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5a8be473de94dcc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5a8be473de94dcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re57b12bc7a074c68"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re57b12bc7a074c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R512247419cf641e7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R512247419cf641e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa12039073e54afa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa12039073e54afa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rda62f07671624d79"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rda62f07671624d79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R061239435699427e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R061239435699427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9244f562ce004849"/>
   </x:sheets>
 </x:workbook>
 </file>
